--- a/기획/SRPG/다이스롤 확률.xlsx
+++ b/기획/SRPG/다이스롤 확률.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\윤정근\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\unityenginebasic_9th\기획\SRPG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C283618C-1561-4B33-900E-6E886AE8172F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB9AD1EE-2252-446F-9DD2-00F9691D29DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10875" yWindow="1770" windowWidth="13305" windowHeight="11295" xr2:uid="{A7999E5D-DE93-44B9-82F3-E30DFEF8C215}"/>
+    <workbookView xWindow="5145" yWindow="1050" windowWidth="21600" windowHeight="11295" xr2:uid="{A7999E5D-DE93-44B9-82F3-E30DFEF8C215}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="54">
   <si>
     <t>약분 및 백분율</t>
   </si>
@@ -429,6 +427,62 @@
   </si>
   <si>
     <t>4~12</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>약분</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>및</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>백분율</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -436,7 +490,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -521,6 +575,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -577,7 +647,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -608,17 +678,20 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -960,57 +1033,58 @@
     <col min="1" max="1" width="9.5" style="1"/>
     <col min="2" max="2" width="3.75" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="9.5" style="1"/>
-    <col min="5" max="5" width="13.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5" style="1"/>
+    <col min="5" max="5" width="15.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.75" style="1" customWidth="1"/>
     <col min="7" max="7" width="3.75" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="9.5" style="1"/>
-    <col min="10" max="10" width="13.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.875" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.5" style="1"/>
     <col min="12" max="12" width="3.75" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="9.5" style="1"/>
-    <col min="15" max="15" width="13.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.875" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="9.5" style="1"/>
     <col min="17" max="17" width="3.75" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="19" width="9.5" style="1"/>
-    <col min="20" max="20" width="13.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.875" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="9.5" style="1"/>
     <col min="22" max="22" width="3.75" style="1" customWidth="1"/>
-    <col min="23" max="24" width="9.5" style="1"/>
-    <col min="25" max="25" width="13.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.5" style="1"/>
+    <col min="25" max="25" width="15.875" style="1" bestFit="1" customWidth="1"/>
     <col min="26" max="16384" width="9.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:25" s="11" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="10" t="s">
+    <row r="3" spans="2:25" s="10" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="G3" s="10" t="s">
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="G3" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="L3" s="10" t="s">
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="L3" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
-      <c r="Q3" s="10" t="s">
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="Q3" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="R3" s="10"/>
-      <c r="S3" s="10"/>
-      <c r="T3" s="10"/>
-      <c r="V3" s="10" t="s">
+      <c r="R3" s="13"/>
+      <c r="S3" s="13"/>
+      <c r="T3" s="13"/>
+      <c r="V3" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="W3" s="10"/>
-      <c r="X3" s="10"/>
-      <c r="Y3" s="10"/>
+      <c r="W3" s="13"/>
+      <c r="X3" s="13"/>
+      <c r="Y3" s="13"/>
     </row>
     <row r="4" spans="2:25" s="9" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="6" t="s">
@@ -1022,8 +1096,8 @@
       <c r="D4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="8" t="s">
-        <v>0</v>
+      <c r="E4" s="14" t="s">
+        <v>53</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>44</v>
@@ -1818,7 +1892,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="2:25" s="13" customFormat="1" ht="31.5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:25" s="11" customFormat="1" ht="31.5" x14ac:dyDescent="0.3">
       <c r="B17" s="12" t="s">
         <v>48</v>
       </c>
@@ -1852,16 +1926,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="L3:O3"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="V3:Y3"/>
     <mergeCell ref="B17:E17"/>
     <mergeCell ref="G17:J17"/>
     <mergeCell ref="L17:O17"/>
     <mergeCell ref="Q17:T17"/>
     <mergeCell ref="V17:Y17"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="L3:O3"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="V3:Y3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
